--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753718880_h_6.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753718880_h_6.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.02797178810939096</v>
+        <v>0.01883437611480588</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008432782635230575</v>
+        <v>0.008419790512046258</v>
       </c>
       <c r="C2" t="n">
-        <v>37877868</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>37877868</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>25848758</v>
+        <v>4255655</v>
       </c>
       <c r="L2" t="n">
-        <v>13793215</v>
+        <v>2213895</v>
       </c>
       <c r="M2" t="n">
-        <v>3119398</v>
+        <v>490702</v>
       </c>
       <c r="N2" t="n">
-        <v>100559</v>
+        <v>14667</v>
       </c>
       <c r="O2" t="n">
-        <v>1884103</v>
+        <v>299124</v>
       </c>
       <c r="P2" t="n">
-        <v>743794</v>
+        <v>118368</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999947547912598</v>
+        <v>0.9999963641166687</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8428394794464111</v>
+        <v>0.8259494304656982</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6911453604698181</v>
+        <v>0.6628561019897461</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6100983619689941</v>
+        <v>0.5743355751037598</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1706753224134445</v>
+        <v>0.1520053893327713</v>
       </c>
       <c r="V2" t="n">
-        <v>0.66862952709198</v>
+        <v>0.6366873383522034</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7797800898551941</v>
+        <v>0.7561566233634949</v>
       </c>
       <c r="X2" t="n">
-        <v>37877868</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,469 +742,469 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>37877868</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>28872412</v>
+        <v>4830872</v>
       </c>
       <c r="AG2" t="n">
-        <v>17836630</v>
+        <v>2998822</v>
       </c>
       <c r="AH2" t="n">
-        <v>4798928</v>
+        <v>802107</v>
       </c>
       <c r="AI2" t="n">
-        <v>353991</v>
+        <v>59151</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2755108</v>
+        <v>459696</v>
       </c>
       <c r="AK2" t="n">
-        <v>1080323</v>
+        <v>180138</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9564692974090576</v>
+        <v>0.9562515616416931</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9113166332244873</v>
+        <v>0.9114683270454407</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8581637144088745</v>
+        <v>0.8577601909637451</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6622001528739929</v>
+        <v>0.6615037322044373</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020119309425354</v>
+        <v>0.9018846154212952</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314349889755249</v>
+        <v>0.9314607977867126</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.006977192966627829</v>
+        <v>0.004456981801839845</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002022202495942296</v>
+        <v>0.002017893641709253</v>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>25848758</v>
+        <v>4255655</v>
       </c>
       <c r="E3" t="n">
-        <v>4190046</v>
+        <v>769747</v>
       </c>
       <c r="F3" t="n">
-        <v>98223</v>
+        <v>17622</v>
       </c>
       <c r="G3" t="n">
-        <v>7957</v>
+        <v>1413</v>
       </c>
       <c r="H3" t="n">
-        <v>6767</v>
+        <v>1105</v>
       </c>
       <c r="I3" t="n">
-        <v>385</v>
+        <v>36</v>
       </c>
       <c r="J3" t="n">
-        <v>60099534</v>
+        <v>10069597</v>
       </c>
       <c r="K3" t="n">
-        <v>63005550</v>
+        <v>10473635</v>
       </c>
       <c r="L3" t="n">
-        <v>72213342</v>
+        <v>11994752</v>
       </c>
       <c r="M3" t="n">
-        <v>90387726</v>
+        <v>15116429</v>
       </c>
       <c r="N3" t="n">
-        <v>96953985</v>
+        <v>16244673</v>
       </c>
       <c r="O3" t="n">
-        <v>93988040</v>
+        <v>15735316</v>
       </c>
       <c r="P3" t="n">
-        <v>96607518</v>
+        <v>16184389</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.857277512550354</v>
+        <v>0.8434422016143799</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7037198543548584</v>
+        <v>0.6718524694442749</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5574007630348206</v>
+        <v>0.524315357208252</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1879639029502869</v>
+        <v>0.1638697683811188</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6165651679039001</v>
+        <v>0.5865234136581421</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6411879062652588</v>
+        <v>0.6119106411933899</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>28872412</v>
+        <v>4830872</v>
       </c>
       <c r="Z3" t="n">
-        <v>1187392</v>
+        <v>199161</v>
       </c>
       <c r="AA3" t="n">
-        <v>51135</v>
+        <v>8614</v>
       </c>
       <c r="AB3" t="n">
-        <v>40793</v>
+        <v>6858</v>
       </c>
       <c r="AC3" t="n">
-        <v>236</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>180</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>60099732</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>66511414</v>
+        <v>11149408</v>
       </c>
       <c r="AG3" t="n">
-        <v>76641422</v>
+        <v>12829512</v>
       </c>
       <c r="AH3" t="n">
-        <v>91588110</v>
+        <v>15347098</v>
       </c>
       <c r="AI3" t="n">
-        <v>97262032</v>
+        <v>16296228</v>
       </c>
       <c r="AJ3" t="n">
-        <v>94622500</v>
+        <v>15855995</v>
       </c>
       <c r="AK3" t="n">
-        <v>96738050</v>
+        <v>16209305</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575573801994324</v>
+        <v>0.9574463367462158</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9100120067596436</v>
+        <v>0.9100549221038818</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8575135469436646</v>
+        <v>0.8570517301559448</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6616765260696411</v>
+        <v>0.6608754992485046</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9015980958938599</v>
+        <v>0.901373565196991</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312928318977356</v>
+        <v>0.9312344789505005</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.06625986209426506</v>
+        <v>0.05172640551346325</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03191410809705398</v>
+        <v>0.03187338455984583</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>4521316</v>
+        <v>844739</v>
       </c>
       <c r="E4" t="n">
-        <v>13793215</v>
+        <v>2213895</v>
       </c>
       <c r="F4" t="n">
-        <v>1113326</v>
+        <v>204182</v>
       </c>
       <c r="G4" t="n">
-        <v>53974</v>
+        <v>10048</v>
       </c>
       <c r="H4" t="n">
-        <v>107602</v>
+        <v>20428</v>
       </c>
       <c r="I4" t="n">
-        <v>10998</v>
+        <v>1918</v>
       </c>
       <c r="J4" t="n">
-        <v>198</v>
+        <v>23</v>
       </c>
       <c r="K4" t="n">
-        <v>4819902</v>
+        <v>896785</v>
       </c>
       <c r="L4" t="n">
-        <v>6163824</v>
+        <v>1126038</v>
       </c>
       <c r="M4" t="n">
-        <v>1993545</v>
+        <v>363680</v>
       </c>
       <c r="N4" t="n">
-        <v>488624</v>
+        <v>81823</v>
       </c>
       <c r="O4" t="n">
-        <v>933755</v>
+        <v>170689</v>
       </c>
       <c r="P4" t="n">
-        <v>210057</v>
+        <v>38171</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999973773956299</v>
+        <v>0.999998152256012</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8499972224235535</v>
+        <v>0.8346041440963745</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6973758935928345</v>
+        <v>0.6673239469528198</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5825603008270264</v>
+        <v>0.5481868386268616</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1789028942584991</v>
+        <v>0.1577147543430328</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6415427923202515</v>
+        <v>0.6105767488479614</v>
       </c>
       <c r="W4" t="n">
-        <v>0.703725278377533</v>
+        <v>0.6764291524887085</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1226769</v>
+        <v>206326</v>
       </c>
       <c r="Z4" t="n">
-        <v>17836630</v>
+        <v>2998822</v>
       </c>
       <c r="AA4" t="n">
-        <v>496804</v>
+        <v>83312</v>
       </c>
       <c r="AB4" t="n">
-        <v>32965</v>
+        <v>5534</v>
       </c>
       <c r="AC4" t="n">
-        <v>6858</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>408</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1314038</v>
+        <v>221012</v>
       </c>
       <c r="AG4" t="n">
-        <v>1735744</v>
+        <v>291278</v>
       </c>
       <c r="AH4" t="n">
-        <v>793161</v>
+        <v>133011</v>
       </c>
       <c r="AI4" t="n">
-        <v>180577</v>
+        <v>30268</v>
       </c>
       <c r="AJ4" t="n">
-        <v>299295</v>
+        <v>50010</v>
       </c>
       <c r="AK4" t="n">
-        <v>79525</v>
+        <v>13255</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9570130109786987</v>
+        <v>0.9568485021591187</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.910663902759552</v>
+        <v>0.9107611179351807</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.85783851146698</v>
+        <v>0.8574058413505554</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6619382500648499</v>
+        <v>0.6611894369125366</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018049240112305</v>
+        <v>0.9016289710998535</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313638806343079</v>
+        <v>0.9313476085662842</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>205647</v>
+        <v>35945</v>
       </c>
       <c r="E5" t="n">
-        <v>1661738</v>
+        <v>298821</v>
       </c>
       <c r="F5" t="n">
-        <v>3119398</v>
+        <v>490702</v>
       </c>
       <c r="G5" t="n">
-        <v>158962</v>
+        <v>26813</v>
       </c>
       <c r="H5" t="n">
-        <v>408051</v>
+        <v>75538</v>
       </c>
       <c r="I5" t="n">
-        <v>42526</v>
+        <v>8071</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>4303390</v>
+        <v>789925</v>
       </c>
       <c r="L5" t="n">
-        <v>5807219</v>
+        <v>1081315</v>
       </c>
       <c r="M5" t="n">
-        <v>2476931</v>
+        <v>445189</v>
       </c>
       <c r="N5" t="n">
-        <v>434432</v>
+        <v>74837</v>
       </c>
       <c r="O5" t="n">
-        <v>1171702</v>
+        <v>210871</v>
       </c>
       <c r="P5" t="n">
-        <v>416231</v>
+        <v>75072</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999979734420776</v>
+        <v>0.9999985694885254</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9068838953971863</v>
+        <v>0.897252082824707</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8778185844421387</v>
+        <v>0.8655365109443665</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9543724656105042</v>
+        <v>0.9507268071174622</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9905788898468018</v>
+        <v>0.9904568791389465</v>
       </c>
       <c r="V5" t="n">
-        <v>0.978510856628418</v>
+        <v>0.9767568111419678</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9936078190803528</v>
+        <v>0.9931016564369202</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>48155</v>
+        <v>8102</v>
       </c>
       <c r="Z5" t="n">
-        <v>510890</v>
+        <v>85827</v>
       </c>
       <c r="AA5" t="n">
-        <v>4798928</v>
+        <v>802107</v>
       </c>
       <c r="AB5" t="n">
-        <v>59714</v>
+        <v>9994</v>
       </c>
       <c r="AC5" t="n">
-        <v>174844</v>
+        <v>29228</v>
       </c>
       <c r="AD5" t="n">
-        <v>3798</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1279736</v>
+        <v>214708</v>
       </c>
       <c r="AG5" t="n">
-        <v>1763804</v>
+        <v>296388</v>
       </c>
       <c r="AH5" t="n">
-        <v>797401</v>
+        <v>133784</v>
       </c>
       <c r="AI5" t="n">
-        <v>181000</v>
+        <v>30353</v>
       </c>
       <c r="AJ5" t="n">
-        <v>300697</v>
+        <v>50299</v>
       </c>
       <c r="AK5" t="n">
-        <v>79702</v>
+        <v>13302</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735268950462341</v>
+        <v>0.9734575748443604</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642821550369263</v>
+        <v>0.9642016291618347</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837660789489746</v>
+        <v>0.9837478399276733</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963095784187317</v>
+        <v>0.9963071942329407</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938762187957764</v>
+        <v>0.9938895702362061</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.998374879360199</v>
+        <v>0.9983822703361511</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>83354</v>
+        <v>14844</v>
       </c>
       <c r="E6" t="n">
-        <v>124190</v>
+        <v>21276</v>
       </c>
       <c r="F6" t="n">
-        <v>161443</v>
+        <v>27323</v>
       </c>
       <c r="G6" t="n">
-        <v>100559</v>
+        <v>14667</v>
       </c>
       <c r="H6" t="n">
-        <v>59155</v>
+        <v>10252</v>
       </c>
       <c r="I6" t="n">
-        <v>6255</v>
+        <v>1136</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>38779</v>
+        <v>6528</v>
       </c>
       <c r="Z6" t="n">
-        <v>32116</v>
+        <v>5399</v>
       </c>
       <c r="AA6" t="n">
-        <v>65335</v>
+        <v>10952</v>
       </c>
       <c r="AB6" t="n">
-        <v>353991</v>
+        <v>59151</v>
       </c>
       <c r="AC6" t="n">
-        <v>41884</v>
+        <v>6993</v>
       </c>
       <c r="AD6" t="n">
-        <v>2886</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>9336</v>
+        <v>1221</v>
       </c>
       <c r="E7" t="n">
-        <v>174793</v>
+        <v>33965</v>
       </c>
       <c r="F7" t="n">
-        <v>585724</v>
+        <v>108110</v>
       </c>
       <c r="G7" t="n">
-        <v>251903</v>
+        <v>40564</v>
       </c>
       <c r="H7" t="n">
-        <v>1884103</v>
+        <v>299124</v>
       </c>
       <c r="I7" t="n">
-        <v>149893</v>
+        <v>27010</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>167</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>4860</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>177905</v>
+        <v>29802</v>
       </c>
       <c r="AB7" t="n">
-        <v>45512</v>
+        <v>7616</v>
       </c>
       <c r="AC7" t="n">
-        <v>2755108</v>
+        <v>459696</v>
       </c>
       <c r="AD7" t="n">
-        <v>72253</v>
+        <v>12043</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>88</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>249</v>
+        <v>36</v>
       </c>
       <c r="E8" t="n">
-        <v>13057</v>
+        <v>2229</v>
       </c>
       <c r="F8" t="n">
-        <v>34829</v>
+        <v>6443</v>
       </c>
       <c r="G8" t="n">
-        <v>15828</v>
+        <v>2985</v>
       </c>
       <c r="H8" t="n">
-        <v>352180</v>
+        <v>63366</v>
       </c>
       <c r="I8" t="n">
-        <v>743794</v>
+        <v>118368</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>168</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>486</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1982</v>
+        <v>331</v>
       </c>
       <c r="AB8" t="n">
-        <v>1593</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>75473</v>
+        <v>12596</v>
       </c>
       <c r="AD8" t="n">
-        <v>1080323</v>
+        <v>180138</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
